--- a/TextGame project/Assets/Resources/Story/11.xlsx
+++ b/TextGame project/Assets/Resources/Story/11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5AD5F1D-2AE5-4AFB-BEEC-C8A9EB4D5428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC03357-18C0-4174-AAC6-C4B4AFB267F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="131">
   <si>
     <t>Name</t>
   </si>
@@ -230,9 +230,6 @@
     <t>（千叶也蹲下来看）</t>
   </si>
   <si>
-    <t>真的诶... 就像... 半阶一样。</t>
-  </si>
-  <si>
     <t>是空的。</t>
   </si>
   <si>
@@ -338,9 +335,6 @@
     <t>为什么... 为什么是我...</t>
   </si>
   <si>
-    <t>（就在这时，密室的门突然 "咔哒" 一声，关上了）</t>
-  </si>
-  <si>
     <t>怎么回事？！</t>
   </si>
   <si>
@@ -417,6 +411,26 @@
   </si>
   <si>
     <t>disappear</t>
+  </si>
+  <si>
+    <t>Wangshushu</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>goto</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yifan</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>真的... 就像... 半阶一样。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（就在这时，密室的门突然 "咔" 一声，关上了）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1056,7 +1070,7 @@
     </row>
     <row r="2" spans="1:22">
       <c r="G2" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H2">
         <v>6</v>
@@ -1072,8 +1086,29 @@
       <c r="C3" t="s">
         <v>24</v>
       </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
       <c r="G3" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="M3" s="1">
+        <v>819.16989999999998</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -1086,23 +1121,17 @@
       <c r="C4" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="J4" s="1">
-        <v>-640.83010000000002</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="M4" s="1">
-        <v>819.16989999999998</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>31</v>
+      <c r="R4">
+        <v>6</v>
+      </c>
+      <c r="T4" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U4" s="1">
+        <v>819.16989999999998</v>
+      </c>
+      <c r="V4" s="1">
+        <v>570</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -1115,11 +1144,17 @@
       <c r="C5" t="s">
         <v>24</v>
       </c>
+      <c r="R5">
+        <v>6</v>
+      </c>
       <c r="T5" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U5" s="1">
         <v>819.16989999999998</v>
+      </c>
+      <c r="V5" s="1">
+        <v>570</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1132,11 +1167,17 @@
       <c r="C6" t="s">
         <v>31</v>
       </c>
+      <c r="R6">
+        <v>6</v>
+      </c>
       <c r="T6" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U6" s="1">
         <v>819.16989999999998</v>
+      </c>
+      <c r="V6" s="1">
+        <v>570</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1149,11 +1190,17 @@
       <c r="C7" t="s">
         <v>24</v>
       </c>
+      <c r="R7">
+        <v>6</v>
+      </c>
       <c r="T7" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U7" s="1">
         <v>819.16989999999998</v>
+      </c>
+      <c r="V7" s="1">
+        <v>570</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1166,11 +1213,17 @@
       <c r="C8" t="s">
         <v>24</v>
       </c>
+      <c r="R8">
+        <v>6</v>
+      </c>
       <c r="T8" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U8" s="1">
         <v>819.16989999999998</v>
+      </c>
+      <c r="V8" s="1">
+        <v>570</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1183,11 +1236,17 @@
       <c r="C9" t="s">
         <v>27</v>
       </c>
+      <c r="R9">
+        <v>6</v>
+      </c>
       <c r="T9" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U9" s="1">
         <v>819.16989999999998</v>
+      </c>
+      <c r="V9" s="1">
+        <v>570</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1200,11 +1259,17 @@
       <c r="C10" t="s">
         <v>31</v>
       </c>
+      <c r="R10">
+        <v>6</v>
+      </c>
       <c r="T10" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U10" s="1">
         <v>819.16989999999998</v>
+      </c>
+      <c r="V10" s="1">
+        <v>570</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1217,11 +1282,17 @@
       <c r="C11" t="s">
         <v>27</v>
       </c>
+      <c r="R11">
+        <v>6</v>
+      </c>
       <c r="T11" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U11" s="1">
         <v>819.16989999999998</v>
+      </c>
+      <c r="V11" s="1">
+        <v>570</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1234,11 +1305,17 @@
       <c r="C12" t="s">
         <v>24</v>
       </c>
+      <c r="R12">
+        <v>6</v>
+      </c>
       <c r="T12" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U12" s="1">
         <v>819.16989999999998</v>
+      </c>
+      <c r="V12" s="1">
+        <v>570</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1251,11 +1328,17 @@
       <c r="C13" t="s">
         <v>24</v>
       </c>
+      <c r="R13">
+        <v>6</v>
+      </c>
       <c r="T13" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U13" s="1">
         <v>819.16989999999998</v>
+      </c>
+      <c r="V13" s="1">
+        <v>570</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1268,11 +1351,17 @@
       <c r="C14" t="s">
         <v>27</v>
       </c>
+      <c r="R14">
+        <v>6</v>
+      </c>
       <c r="T14" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U14" s="1">
         <v>819.16989999999998</v>
+      </c>
+      <c r="V14" s="1">
+        <v>570</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1285,11 +1374,17 @@
       <c r="C15" t="s">
         <v>24</v>
       </c>
+      <c r="R15">
+        <v>6</v>
+      </c>
       <c r="T15" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U15" s="1">
         <v>819.16989999999998</v>
+      </c>
+      <c r="V15" s="1">
+        <v>570</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1302,14 +1397,20 @@
       <c r="C16" t="s">
         <v>24</v>
       </c>
+      <c r="R16">
+        <v>6</v>
+      </c>
       <c r="T16" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U16" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="17" spans="1:21">
+      <c r="V16" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1319,14 +1420,20 @@
       <c r="C17" t="s">
         <v>27</v>
       </c>
+      <c r="R17">
+        <v>6</v>
+      </c>
       <c r="T17" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U17" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="18" spans="1:21">
+      <c r="V17" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -1336,14 +1443,20 @@
       <c r="C18" t="s">
         <v>24</v>
       </c>
+      <c r="R18">
+        <v>6</v>
+      </c>
       <c r="T18" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U18" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="19" spans="1:21">
+      <c r="V18" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1353,14 +1466,20 @@
       <c r="C19" t="s">
         <v>27</v>
       </c>
+      <c r="R19">
+        <v>6</v>
+      </c>
       <c r="T19" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U19" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="20" spans="1:21">
+      <c r="V19" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1370,14 +1489,20 @@
       <c r="C20" t="s">
         <v>24</v>
       </c>
+      <c r="R20">
+        <v>6</v>
+      </c>
       <c r="T20" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U20" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="21" spans="1:21">
+      <c r="V20" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -1387,14 +1512,20 @@
       <c r="C21" t="s">
         <v>24</v>
       </c>
+      <c r="R21">
+        <v>6</v>
+      </c>
       <c r="T21" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U21" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="22" spans="1:21">
+      <c r="V21" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -1404,14 +1535,20 @@
       <c r="C22" t="s">
         <v>27</v>
       </c>
+      <c r="R22">
+        <v>6</v>
+      </c>
       <c r="T22" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U22" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="23" spans="1:21">
+      <c r="V22" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -1421,14 +1558,20 @@
       <c r="C23" t="s">
         <v>24</v>
       </c>
+      <c r="R23">
+        <v>6</v>
+      </c>
       <c r="T23" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U23" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="24" spans="1:21">
+      <c r="V23" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -1438,14 +1581,20 @@
       <c r="C24" t="s">
         <v>27</v>
       </c>
+      <c r="R24">
+        <v>6</v>
+      </c>
       <c r="T24" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U24" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="25" spans="1:21">
+      <c r="V24" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1455,14 +1604,20 @@
       <c r="C25" t="s">
         <v>31</v>
       </c>
+      <c r="R25">
+        <v>6</v>
+      </c>
       <c r="T25" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U25" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="26" spans="1:21">
+      <c r="V25" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -1472,14 +1627,20 @@
       <c r="C26" t="s">
         <v>27</v>
       </c>
+      <c r="R26">
+        <v>6</v>
+      </c>
       <c r="T26" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U26" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="27" spans="1:21">
+      <c r="V26" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" t="s">
         <v>22</v>
       </c>
@@ -1489,14 +1650,20 @@
       <c r="C27" t="s">
         <v>24</v>
       </c>
+      <c r="R27">
+        <v>6</v>
+      </c>
       <c r="T27" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U27" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="28" spans="1:21">
+      <c r="V27" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -1506,14 +1673,20 @@
       <c r="C28" t="s">
         <v>27</v>
       </c>
+      <c r="R28">
+        <v>6</v>
+      </c>
       <c r="T28" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U28" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="29" spans="1:21">
+      <c r="V28" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -1523,14 +1696,20 @@
       <c r="C29" t="s">
         <v>31</v>
       </c>
+      <c r="R29">
+        <v>6</v>
+      </c>
       <c r="T29" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U29" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="30" spans="1:21">
+      <c r="V29" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" t="s">
         <v>22</v>
       </c>
@@ -1540,14 +1719,23 @@
       <c r="C30" t="s">
         <v>24</v>
       </c>
+      <c r="E30">
+        <v>8</v>
+      </c>
+      <c r="R30">
+        <v>6</v>
+      </c>
       <c r="T30" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U30" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="31" spans="1:21">
+      <c r="V30" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" t="s">
         <v>25</v>
       </c>
@@ -1557,14 +1745,20 @@
       <c r="C31" t="s">
         <v>27</v>
       </c>
+      <c r="R31">
+        <v>8</v>
+      </c>
       <c r="T31" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U31" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="32" spans="1:21">
+      <c r="V31" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32" t="s">
         <v>29</v>
       </c>
@@ -1574,14 +1768,20 @@
       <c r="C32" t="s">
         <v>31</v>
       </c>
+      <c r="R32">
+        <v>8</v>
+      </c>
       <c r="T32" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U32" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="33" spans="1:21">
+      <c r="V32" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" t="s">
         <v>22</v>
       </c>
@@ -1591,14 +1791,20 @@
       <c r="C33" t="s">
         <v>24</v>
       </c>
+      <c r="R33">
+        <v>8</v>
+      </c>
       <c r="T33" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U33" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="34" spans="1:21">
+      <c r="V33" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22">
       <c r="A34" t="s">
         <v>29</v>
       </c>
@@ -1608,14 +1814,20 @@
       <c r="C34" t="s">
         <v>31</v>
       </c>
+      <c r="R34">
+        <v>8</v>
+      </c>
       <c r="T34" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U34" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="35" spans="1:21">
+      <c r="V34" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22">
       <c r="A35" t="s">
         <v>22</v>
       </c>
@@ -1625,14 +1837,20 @@
       <c r="C35" t="s">
         <v>31</v>
       </c>
+      <c r="R35">
+        <v>8</v>
+      </c>
       <c r="T35" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U35" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="36" spans="1:21">
+      <c r="V35" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22">
       <c r="A36" t="s">
         <v>25</v>
       </c>
@@ -1642,14 +1860,20 @@
       <c r="C36" t="s">
         <v>27</v>
       </c>
+      <c r="R36">
+        <v>8</v>
+      </c>
       <c r="T36" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U36" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="37" spans="1:21">
+      <c r="V36" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22">
       <c r="A37" t="s">
         <v>29</v>
       </c>
@@ -1659,14 +1883,20 @@
       <c r="C37" t="s">
         <v>31</v>
       </c>
+      <c r="R37">
+        <v>8</v>
+      </c>
       <c r="T37" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U37" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="38" spans="1:21">
+      <c r="V37" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22">
       <c r="A38" t="s">
         <v>29</v>
       </c>
@@ -1676,14 +1906,20 @@
       <c r="C38" t="s">
         <v>31</v>
       </c>
+      <c r="R38">
+        <v>8</v>
+      </c>
       <c r="T38" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U38" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="39" spans="1:21">
+      <c r="V38" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22">
       <c r="A39" t="s">
         <v>22</v>
       </c>
@@ -1693,753 +1929,1032 @@
       <c r="C39" t="s">
         <v>24</v>
       </c>
+      <c r="R39">
+        <v>8</v>
+      </c>
       <c r="T39" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U39" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="40" spans="1:21">
+      <c r="V39" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22">
       <c r="A40" t="s">
         <v>25</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>65</v>
+        <v>129</v>
       </c>
       <c r="C40" t="s">
         <v>27</v>
       </c>
+      <c r="R40">
+        <v>8</v>
+      </c>
       <c r="T40" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U40" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="41" spans="1:21">
+      <c r="V40" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22">
       <c r="A41" t="s">
         <v>29</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C41" t="s">
         <v>31</v>
       </c>
+      <c r="R41">
+        <v>8</v>
+      </c>
       <c r="T41" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U41" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="42" spans="1:21">
+      <c r="V41" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22">
       <c r="A42" t="s">
         <v>22</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42" t="s">
+        <v>24</v>
+      </c>
+      <c r="R42">
+        <v>8</v>
+      </c>
+      <c r="T42" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U42" s="1">
+        <v>819.16989999999998</v>
+      </c>
+      <c r="V42" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22">
+      <c r="A43" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C42" t="s">
-        <v>24</v>
-      </c>
-      <c r="T42" s="1">
-        <v>-640.83010000000002</v>
-      </c>
-      <c r="U42" s="1">
-        <v>819.16989999999998</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21">
-      <c r="A43" t="s">
-        <v>22</v>
-      </c>
-      <c r="B43" s="2" t="s">
+      <c r="C43" t="s">
+        <v>24</v>
+      </c>
+      <c r="R43">
+        <v>8</v>
+      </c>
+      <c r="T43" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U43" s="1">
+        <v>819.16989999999998</v>
+      </c>
+      <c r="V43" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22">
+      <c r="A44" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C43" t="s">
-        <v>24</v>
-      </c>
-      <c r="T43" s="1">
-        <v>-640.83010000000002</v>
-      </c>
-      <c r="U43" s="1">
-        <v>819.16989999999998</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21">
-      <c r="A44" t="s">
-        <v>22</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="C44" t="s">
         <v>24</v>
       </c>
+      <c r="R44">
+        <v>8</v>
+      </c>
       <c r="T44" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U44" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="45" spans="1:21">
+      <c r="V44" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22">
       <c r="A45" t="s">
         <v>25</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C45" t="s">
         <v>27</v>
       </c>
+      <c r="R45">
+        <v>8</v>
+      </c>
       <c r="T45" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U45" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="46" spans="1:21">
+      <c r="V45" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22">
       <c r="A46" t="s">
         <v>29</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C46" t="s">
         <v>31</v>
       </c>
+      <c r="R46">
+        <v>8</v>
+      </c>
       <c r="T46" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U46" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="47" spans="1:21">
+      <c r="V46" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22">
       <c r="A47" t="s">
         <v>22</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" t="s">
+        <v>24</v>
+      </c>
+      <c r="R47">
+        <v>8</v>
+      </c>
+      <c r="T47" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U47" s="1">
+        <v>819.16989999999998</v>
+      </c>
+      <c r="V47" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22">
+      <c r="A48" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C47" t="s">
-        <v>24</v>
-      </c>
-      <c r="T47" s="1">
-        <v>-640.83010000000002</v>
-      </c>
-      <c r="U47" s="1">
-        <v>819.16989999999998</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21">
-      <c r="A48" t="s">
-        <v>22</v>
-      </c>
-      <c r="B48" s="2" t="s">
+      <c r="C48" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48">
+        <v>6</v>
+      </c>
+      <c r="R48">
+        <v>8</v>
+      </c>
+      <c r="T48" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U48" s="1">
+        <v>819.16989999999998</v>
+      </c>
+      <c r="V48" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22">
+      <c r="A49" t="s">
+        <v>22</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C48" t="s">
-        <v>24</v>
-      </c>
-      <c r="T48" s="1">
-        <v>-640.83010000000002</v>
-      </c>
-      <c r="U48" s="1">
-        <v>819.16989999999998</v>
-      </c>
-    </row>
-    <row r="49" spans="1:21">
-      <c r="A49" t="s">
-        <v>22</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="C49" t="s">
         <v>24</v>
       </c>
+      <c r="R49">
+        <v>6</v>
+      </c>
       <c r="T49" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U49" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="50" spans="1:21">
+      <c r="V49" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22">
       <c r="A50" t="s">
         <v>25</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
       </c>
+      <c r="R50">
+        <v>6</v>
+      </c>
       <c r="T50" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U50" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="51" spans="1:21">
+      <c r="V50" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22">
       <c r="A51" t="s">
         <v>22</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C51" t="s">
+        <v>24</v>
+      </c>
+      <c r="R51">
+        <v>6</v>
+      </c>
+      <c r="T51" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U51" s="1">
+        <v>819.16989999999998</v>
+      </c>
+      <c r="V51" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22">
+      <c r="A52" t="s">
+        <v>22</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C51" t="s">
-        <v>24</v>
-      </c>
-      <c r="T51" s="1">
-        <v>-640.83010000000002</v>
-      </c>
-      <c r="U51" s="1">
-        <v>819.16989999999998</v>
-      </c>
-    </row>
-    <row r="52" spans="1:21">
-      <c r="A52" t="s">
-        <v>22</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C52" t="s">
         <v>24</v>
       </c>
+      <c r="R52">
+        <v>6</v>
+      </c>
       <c r="T52" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U52" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="53" spans="1:21">
+      <c r="V52" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22">
       <c r="A53" t="s">
         <v>25</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C53" t="s">
         <v>27</v>
       </c>
+      <c r="R53">
+        <v>6</v>
+      </c>
       <c r="T53" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U53" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="54" spans="1:21">
+      <c r="V53" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22">
       <c r="A54" t="s">
         <v>22</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C54" t="s">
         <v>24</v>
       </c>
+      <c r="R54">
+        <v>6</v>
+      </c>
       <c r="T54" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U54" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="55" spans="1:21">
+      <c r="V54" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22">
       <c r="A55" t="s">
         <v>29</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C55" t="s">
         <v>31</v>
       </c>
+      <c r="R55">
+        <v>6</v>
+      </c>
       <c r="T55" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U55" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="56" spans="1:21">
+      <c r="V55" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22">
       <c r="A56" t="s">
         <v>22</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C56" t="s">
         <v>24</v>
       </c>
+      <c r="R56">
+        <v>6</v>
+      </c>
       <c r="T56" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U56" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="57" spans="1:21">
+      <c r="V56" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22">
       <c r="A57" t="s">
         <v>29</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C57" t="s">
         <v>31</v>
       </c>
+      <c r="R57">
+        <v>6</v>
+      </c>
       <c r="T57" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U57" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="58" spans="1:21">
+      <c r="V57" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22">
       <c r="A58" t="s">
         <v>22</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C58" t="s">
+        <v>24</v>
+      </c>
+      <c r="R58">
+        <v>6</v>
+      </c>
+      <c r="T58" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U58" s="1">
+        <v>819.16989999999998</v>
+      </c>
+      <c r="V58" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22">
+      <c r="A59" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C58" t="s">
-        <v>24</v>
-      </c>
-      <c r="T58" s="1">
-        <v>-640.83010000000002</v>
-      </c>
-      <c r="U58" s="1">
-        <v>819.16989999999998</v>
-      </c>
-    </row>
-    <row r="59" spans="1:21">
-      <c r="A59" t="s">
-        <v>22</v>
-      </c>
-      <c r="B59" s="2" t="s">
+      <c r="C59" t="s">
+        <v>24</v>
+      </c>
+      <c r="R59">
+        <v>6</v>
+      </c>
+      <c r="T59" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U59" s="1">
+        <v>819.16989999999998</v>
+      </c>
+      <c r="V59" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22">
+      <c r="A60" t="s">
+        <v>22</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C59" t="s">
-        <v>24</v>
-      </c>
-      <c r="T59" s="1">
-        <v>-640.83010000000002</v>
-      </c>
-      <c r="U59" s="1">
-        <v>819.16989999999998</v>
-      </c>
-    </row>
-    <row r="60" spans="1:21">
-      <c r="A60" t="s">
-        <v>22</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="C60" t="s">
         <v>24</v>
       </c>
+      <c r="R60">
+        <v>6</v>
+      </c>
       <c r="T60" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U60" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="61" spans="1:21">
+      <c r="V60" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22">
       <c r="A61" t="s">
         <v>25</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C61" t="s">
         <v>27</v>
       </c>
+      <c r="R61">
+        <v>6</v>
+      </c>
       <c r="T61" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U61" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="62" spans="1:21">
+      <c r="V61" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22">
       <c r="A62" t="s">
         <v>22</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C62" t="s">
+        <v>24</v>
+      </c>
+      <c r="R62">
+        <v>6</v>
+      </c>
+      <c r="T62" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U62" s="1">
+        <v>819.16989999999998</v>
+      </c>
+      <c r="V62" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22">
+      <c r="A63" t="s">
+        <v>22</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C62" t="s">
-        <v>24</v>
-      </c>
-      <c r="T62" s="1">
-        <v>-640.83010000000002</v>
-      </c>
-      <c r="U62" s="1">
-        <v>819.16989999999998</v>
-      </c>
-    </row>
-    <row r="63" spans="1:21">
-      <c r="A63" t="s">
-        <v>22</v>
-      </c>
-      <c r="B63" s="2" t="s">
+      <c r="C63" t="s">
+        <v>24</v>
+      </c>
+      <c r="R63">
+        <v>6</v>
+      </c>
+      <c r="T63" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U63" s="1">
+        <v>819.16989999999998</v>
+      </c>
+      <c r="V63" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22">
+      <c r="A64" t="s">
+        <v>22</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C63" t="s">
-        <v>24</v>
-      </c>
-      <c r="T63" s="1">
-        <v>-640.83010000000002</v>
-      </c>
-      <c r="U63" s="1">
-        <v>819.16989999999998</v>
-      </c>
-    </row>
-    <row r="64" spans="1:21">
-      <c r="A64" t="s">
-        <v>22</v>
-      </c>
-      <c r="B64" s="2" t="s">
+      <c r="C64" t="s">
+        <v>24</v>
+      </c>
+      <c r="R64">
+        <v>6</v>
+      </c>
+      <c r="T64" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U64" s="1">
+        <v>819.16989999999998</v>
+      </c>
+      <c r="V64" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22">
+      <c r="A65" t="s">
+        <v>22</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C64" t="s">
-        <v>24</v>
-      </c>
-      <c r="T64" s="1">
-        <v>-640.83010000000002</v>
-      </c>
-      <c r="U64" s="1">
-        <v>819.16989999999998</v>
-      </c>
-    </row>
-    <row r="65" spans="1:21">
-      <c r="A65" t="s">
-        <v>22</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="C65" t="s">
         <v>24</v>
       </c>
+      <c r="R65">
+        <v>6</v>
+      </c>
       <c r="T65" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U65" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="66" spans="1:21">
+      <c r="V65" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22">
       <c r="A66" t="s">
         <v>25</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C66" t="s">
         <v>27</v>
       </c>
+      <c r="R66">
+        <v>6</v>
+      </c>
       <c r="T66" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U66" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="67" spans="1:21">
+      <c r="V66" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22">
       <c r="A67" t="s">
         <v>22</v>
       </c>
       <c r="B67" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C67" t="s">
+        <v>24</v>
+      </c>
+      <c r="R67">
+        <v>6</v>
+      </c>
+      <c r="T67" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U67" s="1">
+        <v>819.16989999999998</v>
+      </c>
+      <c r="V67" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22">
+      <c r="A68" t="s">
+        <v>22</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C67" t="s">
-        <v>24</v>
-      </c>
-      <c r="T67" s="1">
-        <v>-640.83010000000002</v>
-      </c>
-      <c r="U67" s="1">
-        <v>819.16989999999998</v>
-      </c>
-    </row>
-    <row r="68" spans="1:21">
-      <c r="A68" t="s">
-        <v>22</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="C68" t="s">
         <v>24</v>
       </c>
+      <c r="R68">
+        <v>6</v>
+      </c>
       <c r="T68" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U68" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="69" spans="1:21">
+      <c r="V68" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22">
       <c r="A69" t="s">
         <v>25</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C69" t="s">
         <v>27</v>
       </c>
+      <c r="R69">
+        <v>6</v>
+      </c>
       <c r="T69" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U69" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="70" spans="1:21">
+      <c r="V69" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22">
       <c r="A70" t="s">
         <v>22</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C70" t="s">
         <v>24</v>
       </c>
+      <c r="R70">
+        <v>6</v>
+      </c>
       <c r="T70" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U70" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="71" spans="1:21">
+      <c r="V70" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22">
       <c r="A71" t="s">
         <v>25</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C71" t="s">
         <v>27</v>
       </c>
+      <c r="R71">
+        <v>6</v>
+      </c>
       <c r="T71" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U71" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="72" spans="1:21">
+      <c r="V71" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22">
       <c r="A72" t="s">
         <v>22</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C72" t="s">
         <v>24</v>
       </c>
+      <c r="R72">
+        <v>6</v>
+      </c>
       <c r="T72" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U72" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="73" spans="1:21">
+      <c r="V72" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22">
       <c r="A73" t="s">
         <v>25</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C73" t="s">
         <v>27</v>
       </c>
+      <c r="R73">
+        <v>6</v>
+      </c>
       <c r="T73" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U73" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="74" spans="1:21">
+      <c r="V73" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22">
       <c r="A74" t="s">
         <v>29</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C74" t="s">
         <v>31</v>
       </c>
+      <c r="R74">
+        <v>6</v>
+      </c>
       <c r="T74" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U74" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="75" spans="1:21">
+      <c r="V74" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22">
       <c r="A75" t="s">
         <v>25</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C75" t="s">
         <v>27</v>
       </c>
+      <c r="R75">
+        <v>6</v>
+      </c>
       <c r="T75" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U75" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="76" spans="1:21">
+      <c r="V75" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22">
       <c r="A76" t="s">
         <v>22</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="C76" t="s">
         <v>24</v>
       </c>
+      <c r="R76">
+        <v>6</v>
+      </c>
       <c r="T76" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U76" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="77" spans="1:21">
+      <c r="V76" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22">
       <c r="A77" t="s">
         <v>25</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C77" t="s">
         <v>27</v>
       </c>
+      <c r="R77">
+        <v>6</v>
+      </c>
       <c r="T77" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U77" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="78" spans="1:21">
+      <c r="V77" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22">
       <c r="A78" t="s">
         <v>22</v>
       </c>
       <c r="B78" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C78" t="s">
+        <v>24</v>
+      </c>
+      <c r="R78">
+        <v>6</v>
+      </c>
+      <c r="T78" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U78" s="1">
+        <v>819.16989999999998</v>
+      </c>
+      <c r="V78" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22">
+      <c r="A79" t="s">
+        <v>22</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C79" t="s">
+        <v>24</v>
+      </c>
+      <c r="R79">
+        <v>6</v>
+      </c>
+      <c r="T79" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U79" s="1">
+        <v>819.16989999999998</v>
+      </c>
+      <c r="V79" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22">
+      <c r="A80" t="s">
         <v>103</v>
       </c>
-      <c r="C78" t="s">
-        <v>24</v>
-      </c>
-      <c r="T78" s="1">
-        <v>-640.83010000000002</v>
-      </c>
-      <c r="U78" s="1">
-        <v>819.16989999999998</v>
-      </c>
-    </row>
-    <row r="79" spans="1:21">
-      <c r="A79" t="s">
-        <v>22</v>
-      </c>
-      <c r="B79" s="2" t="s">
+      <c r="B80" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C79" t="s">
-        <v>24</v>
-      </c>
-      <c r="T79" s="1">
-        <v>-640.83010000000002</v>
-      </c>
-      <c r="U79" s="1">
-        <v>819.16989999999998</v>
-      </c>
-    </row>
-    <row r="80" spans="1:21">
-      <c r="A80" t="s">
+      <c r="C80" t="s">
         <v>105</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="O80" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="P80" s="1">
+        <v>570</v>
+      </c>
+      <c r="Q80" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="R80">
+        <v>6</v>
+      </c>
+      <c r="T80" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U80" s="1">
+        <v>819.16989999999998</v>
+      </c>
+      <c r="V80" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22">
+      <c r="A81" t="s">
+        <v>22</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C80" t="s">
-        <v>107</v>
-      </c>
-      <c r="T80" s="1">
-        <v>-640.83010000000002</v>
-      </c>
-      <c r="U80" s="1">
-        <v>819.16989999999998</v>
-      </c>
-    </row>
-    <row r="81" spans="1:21">
-      <c r="A81" t="s">
-        <v>22</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="C81" t="s">
         <v>24</v>
       </c>
+      <c r="R81">
+        <v>6</v>
+      </c>
       <c r="T81" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U81" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="82" spans="1:21">
+      <c r="V81" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22">
       <c r="A82" t="s">
         <v>25</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C82" t="s">
         <v>27</v>
       </c>
+      <c r="R82">
+        <v>6</v>
+      </c>
       <c r="T82" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U82" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="83" spans="1:21">
+      <c r="V82" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22">
       <c r="A83" t="s">
+        <v>103</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C83" t="s">
         <v>105</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C83" t="s">
-        <v>107</v>
+      <c r="R83">
+        <v>6</v>
       </c>
       <c r="T83" s="1">
         <v>-640.83010000000002</v>
@@ -2447,118 +2962,169 @@
       <c r="U83" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="84" spans="1:21">
+      <c r="V83" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22">
       <c r="A84" t="s">
         <v>29</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C84" t="s">
         <v>31</v>
       </c>
+      <c r="R84">
+        <v>6</v>
+      </c>
       <c r="T84" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U84" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="85" spans="1:21">
+      <c r="V84" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22">
       <c r="A85" t="s">
+        <v>103</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C85" t="s">
         <v>105</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="R85">
+        <v>6</v>
+      </c>
+      <c r="T85" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U85" s="1">
+        <v>819.16989999999998</v>
+      </c>
+      <c r="V85" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22">
+      <c r="A86" t="s">
+        <v>22</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C86" t="s">
+        <v>24</v>
+      </c>
+      <c r="R86">
+        <v>6</v>
+      </c>
+      <c r="T86" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U86" s="1">
+        <v>819.16989999999998</v>
+      </c>
+      <c r="V86" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22">
+      <c r="A87" t="s">
+        <v>103</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C85" t="s">
-        <v>107</v>
-      </c>
-      <c r="T85" s="1">
-        <v>-640.83010000000002</v>
-      </c>
-      <c r="U85" s="1">
-        <v>819.16989999999998</v>
-      </c>
-    </row>
-    <row r="86" spans="1:21">
-      <c r="A86" t="s">
-        <v>22</v>
-      </c>
-      <c r="B86" s="2" t="s">
+      <c r="C87" t="s">
+        <v>105</v>
+      </c>
+      <c r="R87">
+        <v>6</v>
+      </c>
+      <c r="T87" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="U87" s="1">
+        <v>819.16989999999998</v>
+      </c>
+      <c r="V87" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22">
+      <c r="A88" t="s">
+        <v>22</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C86" t="s">
-        <v>24</v>
-      </c>
-      <c r="T86" s="1">
-        <v>-640.83010000000002</v>
-      </c>
-      <c r="U86" s="1">
-        <v>819.16989999999998</v>
-      </c>
-    </row>
-    <row r="87" spans="1:21">
-      <c r="A87" t="s">
-        <v>105</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C87" t="s">
-        <v>107</v>
-      </c>
-      <c r="T87" s="1">
-        <v>-640.83010000000002</v>
-      </c>
-      <c r="U87" s="1">
-        <v>819.16989999999998</v>
-      </c>
-    </row>
-    <row r="88" spans="1:21">
-      <c r="A88" t="s">
-        <v>22</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="C88" t="s">
         <v>24</v>
       </c>
+      <c r="R88">
+        <v>6</v>
+      </c>
       <c r="T88" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U88" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="89" spans="1:21">
+      <c r="V88" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22">
       <c r="A89" t="s">
         <v>25</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C89" t="s">
         <v>27</v>
       </c>
+      <c r="R89">
+        <v>6</v>
+      </c>
       <c r="T89" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U89" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="90" spans="1:21">
+      <c r="V89" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22">
       <c r="A90" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C90" t="s">
-        <v>107</v>
+        <v>115</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="O90" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="P90" s="1">
+        <v>570</v>
+      </c>
+      <c r="Q90" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="R90">
+        <v>6</v>
       </c>
       <c r="T90" s="1">
         <v>-640.83010000000002</v>
@@ -2566,33 +3132,45 @@
       <c r="U90" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="91" spans="1:21">
+      <c r="V90" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22">
       <c r="A91" t="s">
         <v>25</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C91" t="s">
         <v>27</v>
       </c>
+      <c r="R91">
+        <v>6</v>
+      </c>
       <c r="T91" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U91" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="92" spans="1:21">
+      <c r="V91" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22">
       <c r="A92" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C92" t="s">
-        <v>107</v>
+        <v>117</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="R92">
+        <v>6</v>
       </c>
       <c r="T92" s="1">
         <v>-640.83010000000002</v>
@@ -2600,101 +3178,137 @@
       <c r="U92" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="93" spans="1:21">
+      <c r="V92" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22">
       <c r="A93" t="s">
         <v>22</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C93" t="s">
         <v>24</v>
       </c>
+      <c r="R93">
+        <v>6</v>
+      </c>
       <c r="T93" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U93" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="94" spans="1:21">
+      <c r="V93" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22">
       <c r="A94" t="s">
         <v>29</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C94" t="s">
         <v>31</v>
       </c>
+      <c r="R94">
+        <v>6</v>
+      </c>
       <c r="T94" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U94" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="95" spans="1:21">
+      <c r="V94" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22">
       <c r="A95" t="s">
         <v>25</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C95" t="s">
         <v>27</v>
       </c>
+      <c r="R95">
+        <v>6</v>
+      </c>
       <c r="T95" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U95" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="96" spans="1:21">
+      <c r="V95" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22">
       <c r="A96" t="s">
         <v>29</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C96" t="s">
         <v>31</v>
       </c>
+      <c r="R96">
+        <v>6</v>
+      </c>
       <c r="T96" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U96" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="97" spans="1:21">
+      <c r="V96" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="97" spans="1:22">
       <c r="A97" t="s">
         <v>22</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C97" t="s">
         <v>24</v>
       </c>
+      <c r="R97">
+        <v>6</v>
+      </c>
       <c r="T97" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="U97" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="98" spans="1:21">
+      <c r="V97" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="98" spans="1:22">
       <c r="A98" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C98" t="s">
-        <v>107</v>
+        <v>123</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="R98">
+        <v>6</v>
       </c>
       <c r="T98" s="1">
         <v>-640.83010000000002</v>
@@ -2702,14 +3316,22 @@
       <c r="U98" s="1">
         <v>819.16989999999998</v>
       </c>
-    </row>
-    <row r="99" spans="1:21">
-      <c r="A99" s="5"/>
+      <c r="V98" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="99" spans="1:22">
+      <c r="A99" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B99">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C106" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C89 C91 C93:C97 C99:C106" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Qianye,White,Linshen,Wangshushu"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A98 A100:A157" xr:uid="{00000000-0002-0000-0000-000001000000}">

--- a/TextGame project/Assets/Resources/Story/11.xlsx
+++ b/TextGame project/Assets/Resources/Story/11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC03357-18C0-4174-AAC6-C4B4AFB267F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C0D1708-9729-4C3F-B9C0-D1BCDAC3BA43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -113,9 +113,6 @@
     <t>千叶</t>
   </si>
   <si>
-    <t>好黑啊...</t>
-  </si>
-  <si>
     <t>Qianye</t>
   </si>
   <si>
@@ -125,9 +122,6 @@
     <t>林深</t>
   </si>
   <si>
-    <t>小心点。</t>
-  </si>
-  <si>
     <t>Linshen</t>
   </si>
   <si>
@@ -137,102 +131,48 @@
     <t>（千叶注意到墙上有一些奇怪的痕迹）</t>
   </si>
   <si>
-    <t>墙上那是什么... 抓痕吗？</t>
-  </si>
-  <si>
-    <t>... 嗯。</t>
-  </si>
-  <si>
-    <t>是谁... 抓的...</t>
-  </si>
-  <si>
     <t>（林深没回答，继续往里走）</t>
   </si>
   <si>
     <t>（千叶跟在他后面，紧紧抓着他的衣角）</t>
   </si>
   <si>
-    <t>那个是...</t>
-  </si>
-  <si>
     <t>（她走过去，拿起那个玩偶）</t>
   </si>
   <si>
     <t>（是一个很旧的兔子玩偶，耳朵都快掉了）</t>
   </si>
   <si>
-    <t>这是... 小柚的玩偶...</t>
-  </si>
-  <si>
     <t>（她的眼泪又掉了下来）</t>
   </si>
   <si>
-    <t>这个玩偶... 妹妹走到哪儿都带着的... 怎么会在这里...</t>
-  </si>
-  <si>
     <t>（她把玩偶翻过来，看到背面有几行用线缝的字）</t>
   </si>
   <si>
     <t>（是用很幼稚的针法缝的，歪歪扭扭的）</t>
   </si>
   <si>
-    <t>"姐姐... 钟楼... 十三阶... 坏人..."</t>
-  </si>
-  <si>
     <t>（她愣住了）</t>
   </si>
   <si>
-    <t>钟楼... 第十三阶...</t>
-  </si>
-  <si>
-    <t>这是...</t>
-  </si>
-  <si>
-    <t>是小柚留的... 这是我们小时候玩的暗号... 只有我们两个才看得懂...</t>
-  </si>
-  <si>
     <t>（她擦了擦眼泪，眼神变得坚定）</t>
   </si>
   <si>
-    <t>妹妹在告诉我们... 真相在钟楼里。</t>
-  </si>
-  <si>
-    <t>走，去钟楼。</t>
-  </si>
-  <si>
     <t>（两人来到钟楼，螺旋楼梯向上延伸，巨大的齿轮和钟摆在晃动）</t>
   </si>
   <si>
-    <t>好高啊...</t>
-  </si>
-  <si>
-    <t>传说中的第十三阶... 我们数数看。</t>
-  </si>
-  <si>
     <t>（两人开始数台阶）</t>
   </si>
   <si>
-    <t>一、二、三... 十、十一、十二...</t>
-  </si>
-  <si>
     <t>（数到十二阶，就到平台了）</t>
   </si>
   <si>
-    <t>只有十二阶啊... 第十三阶在哪里？</t>
-  </si>
-  <si>
-    <t>... 不对。</t>
-  </si>
-  <si>
     <t>这一阶比其他的矮一点，而且颜色也不一样。</t>
   </si>
   <si>
     <t>（千叶也蹲下来看）</t>
   </si>
   <si>
-    <t>是空的。</t>
-  </si>
-  <si>
     <t>（他用力按了一下）</t>
   </si>
   <si>
@@ -242,12 +182,6 @@
     <t>（旁边的墙壁移开，露出了一个隐藏的密室）</t>
   </si>
   <si>
-    <t>真的有密室！</t>
-  </si>
-  <si>
-    <t>小心。</t>
-  </si>
-  <si>
     <t>（两人走进密室）</t>
   </si>
   <si>
@@ -257,30 +191,18 @@
     <t>（都是... 女孩子的照片）</t>
   </si>
   <si>
-    <t>这些是...</t>
-  </si>
-  <si>
     <t>（她走近看，照片上的女孩子都被用红笔圈了脸，有的还写了日期）</t>
   </si>
   <si>
     <t>（有的照片上，女孩子在笑；有的照片上，女孩子在哭）</t>
   </si>
   <si>
-    <t>这些都是... 受害者吗...</t>
-  </si>
-  <si>
     <t>（林深翻着桌上的相册）</t>
   </si>
   <si>
-    <t>这里有所有失踪女生的资料...</t>
-  </si>
-  <si>
     <t>（他翻到一页，停住了）</t>
   </si>
   <si>
-    <t>千叶，你看。</t>
-  </si>
-  <si>
     <t>（千叶接过相册，那一页上，是妹妹的照片）</t>
   </si>
   <si>
@@ -290,9 +212,6 @@
     <t>（旁边写着日期，正是妹妹失踪那天）</t>
   </si>
   <si>
-    <t>小柚...</t>
-  </si>
-  <si>
     <t>（她继续往后翻）</t>
   </si>
   <si>
@@ -305,39 +224,18 @@
     <t>（千叶看到那张脸，整个人都僵住了）</t>
   </si>
   <si>
-    <t>不... 不可能...</t>
-  </si>
-  <si>
     <t>（照片上的人，是住在她家隔壁的王叔叔）</t>
   </si>
   <si>
     <t>（也是她学校的教导主任）</t>
   </si>
   <si>
-    <t>怎么会... 怎么会是王叔叔...</t>
-  </si>
-  <si>
     <t>（她摇着头，不敢相信）</t>
   </si>
   <si>
-    <t>他平时对我那么好... 还经常给我送吃的... 还提醒我注意安全...</t>
-  </si>
-  <si>
     <t>（她想起了什么）</t>
   </si>
   <si>
-    <t>难道说... 学校里的传闻... 也是他放出来的？</t>
-  </si>
-  <si>
-    <t>很有可能。他故意放出消息，引诱你来这里。</t>
-  </si>
-  <si>
-    <t>为什么... 为什么是我...</t>
-  </si>
-  <si>
-    <t>怎么回事？！</t>
-  </si>
-  <si>
     <t>（门外传来了一个声音）</t>
   </si>
   <si>
@@ -347,66 +245,24 @@
     <t>王叔叔</t>
   </si>
   <si>
-    <t>千叶，你终于来了。</t>
-  </si>
-  <si>
     <t>Wangshushu</t>
   </si>
   <si>
     <t>（千叶的脸瞬间白了）</t>
   </si>
   <si>
-    <t>王、王叔叔...？</t>
-  </si>
-  <si>
-    <t>我等这一天，等了好久啊。</t>
-  </si>
-  <si>
-    <t>你是谁？</t>
-  </si>
-  <si>
-    <t>我是谁不重要。重要的是... 你们今天，都别想走了。</t>
-  </si>
-  <si>
     <t>（他的声音里带着笑意，却让人不寒而栗）</t>
   </si>
   <si>
-    <t>特别是你，千叶... 你和你妹妹，长得真像啊。</t>
-  </si>
-  <si>
     <t>（千叶听到这句话，浑身发抖，眼泪止不住地流）</t>
   </si>
   <si>
-    <t>你... 你把小柚怎么了...</t>
-  </si>
-  <si>
-    <t>你说呢？</t>
-  </si>
-  <si>
-    <t>你这个变态！</t>
-  </si>
-  <si>
-    <t>变态？呵呵... 等你见识到什么是真正的变态，再说也不迟。</t>
-  </si>
-  <si>
     <t>（门开始慢慢打开）</t>
   </si>
   <si>
-    <t>千叶，听着。一会儿我冲出去拦住他，你趁机跑，跑到有信号的地方报警。知道吗？</t>
-  </si>
-  <si>
-    <t>不行！我不走！要走一起走！</t>
-  </si>
-  <si>
-    <t>没时间了！听我的！</t>
-  </si>
-  <si>
     <t>（门完全打开了，王叔叔站在门口，脸上带着诡异的微笑）</t>
   </si>
   <si>
-    <t>两个小朋友，玩够了吗？</t>
-  </si>
-  <si>
     <t>appearAt</t>
   </si>
   <si>
@@ -425,11 +281,203 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>真的... 就像... 半阶一样。</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>（就在这时，密室的门突然 "咔" 一声，关上了）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（小声）好黑啊...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（警惕地观察四周）小心点。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（害怕）墙上那是什么... 抓痕吗？</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（表情凝重）... 嗯。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（浑身发冷）是谁... 抓的...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（愣住）那个是...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（声音发抖）这是... 小柚的玩偶...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（哽咽）这个玩偶... 妹妹走到哪儿都带着的... 怎么会在这里...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（念出来）"姐姐... 钟楼... 十三阶... 坏人..."</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（喃喃）钟楼... 第十三阶...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（走过来，看到玩偶上的字）这是...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（眼泪模糊了视线）是小柚留的... 这是我们小时候玩的暗号... 只有我们两个才看得懂...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（坚定）妹妹在告诉我们... 真相在钟楼里。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（点头）走，去钟楼。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（抬头看）好高啊...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（看着楼梯）传说中的第十三阶... 我们数数看。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（数着）一、二、三... 十、十一、十二...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（疑惑）只有十二阶啊... 第十三阶在哪里？</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（蹲下来，看着最下面的一阶）... 不对。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（惊讶）真的... 就像... 半阶一样。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（试着踩了踩那半阶）是空的。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（震惊）真的有密室！</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（警惕）小心。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（捂住嘴）这些是...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（浑身发冷）这些都是... 受害者吗...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（声音低沉）这里有所有失踪女生的资料...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（把相册递给千叶）千叶，你看。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（眼泪掉了下来）小柚...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（不敢相信）不... 不可能...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（声音发抖）怎么会... 怎么会是王叔叔...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（喃喃）他平时对我那么好... 还经常给我送吃的... 还提醒我注意安全...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（震惊）难道说... 学校里的传闻... 也是他放出来的？</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（点头，表情凝重）很有可能。他故意放出消息，引诱你来这里。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（浑身发冷）为什么... 为什么是我...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（吓了一跳）怎么回事？！</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（画外音，微笑着）千叶，你终于来了。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（惊恐）王、王叔叔...？</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（笑着说）我等这一天，等了好久啊。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（挡在千叶前面，警惕地看着门口）你是谁？</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（慢悠悠地说）我是谁不重要。重要的是... 你们今天，都别想走了。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（轻声）特别是你，千叶... 你和你妹妹，长得真像啊。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（带着哭腔）你... 你把小柚怎么了...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（笑着）你说呢？</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（愤怒又悲伤）你这个变态！</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（语气变得阴冷）变态？呵呵... 等你见识到什么是真正的变态，再说也不迟。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（低声对千叶说）千叶，听着。一会儿我冲出去拦住他，你趁机跑，跑到有信号的地方报警。知道吗？</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（摇头）不行！我不走！要走一起走！</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（严肃）没时间了！听我的！</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>（微笑着）两个小朋友，玩够了吗？</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1070,7 +1118,7 @@
     </row>
     <row r="2" spans="1:22">
       <c r="G2" s="4" t="s">
-        <v>124</v>
+        <v>76</v>
       </c>
       <c r="H2">
         <v>6</v>
@@ -1089,26 +1137,29 @@
       <c r="E3">
         <v>6</v>
       </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
       <c r="G3" s="4" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>124</v>
+        <v>76</v>
       </c>
       <c r="J3" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>124</v>
+        <v>76</v>
       </c>
       <c r="M3" s="1">
         <v>819.16989999999998</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -1116,13 +1167,16 @@
         <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" t="s">
         <v>26</v>
       </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
       <c r="R4">
         <v>6</v>
+      </c>
+      <c r="S4">
+        <v>2</v>
       </c>
       <c r="T4" s="1">
         <v>-640.83010000000002</v>
@@ -1139,13 +1193,16 @@
         <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
         <v>24</v>
       </c>
       <c r="R5">
         <v>6</v>
+      </c>
+      <c r="S5">
+        <v>2</v>
       </c>
       <c r="T5" s="1">
         <v>-640.83010000000002</v>
@@ -1159,16 +1216,19 @@
     </row>
     <row r="6" spans="1:22">
       <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
       <c r="R6">
         <v>6</v>
+      </c>
+      <c r="S6">
+        <v>2</v>
       </c>
       <c r="T6" s="1">
         <v>-640.83010000000002</v>
@@ -1185,13 +1245,16 @@
         <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
         <v>24</v>
       </c>
       <c r="R7">
         <v>6</v>
+      </c>
+      <c r="S7">
+        <v>2</v>
       </c>
       <c r="T7" s="1">
         <v>-640.83010000000002</v>
@@ -1208,13 +1271,16 @@
         <v>22</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
       </c>
       <c r="R8">
         <v>6</v>
+      </c>
+      <c r="S8">
+        <v>2</v>
       </c>
       <c r="T8" s="1">
         <v>-640.83010000000002</v>
@@ -1231,13 +1297,16 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R9">
         <v>6</v>
+      </c>
+      <c r="S9">
+        <v>2</v>
       </c>
       <c r="T9" s="1">
         <v>-640.83010000000002</v>
@@ -1251,16 +1320,19 @@
     </row>
     <row r="10" spans="1:22">
       <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
       <c r="R10">
         <v>6</v>
+      </c>
+      <c r="S10">
+        <v>2</v>
       </c>
       <c r="T10" s="1">
         <v>-640.83010000000002</v>
@@ -1277,13 +1349,16 @@
         <v>25</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R11">
         <v>6</v>
+      </c>
+      <c r="S11">
+        <v>2</v>
       </c>
       <c r="T11" s="1">
         <v>-640.83010000000002</v>
@@ -1300,13 +1375,16 @@
         <v>22</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
         <v>24</v>
       </c>
       <c r="R12">
         <v>6</v>
+      </c>
+      <c r="S12">
+        <v>2</v>
       </c>
       <c r="T12" s="1">
         <v>-640.83010000000002</v>
@@ -1323,13 +1401,16 @@
         <v>22</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
         <v>24</v>
       </c>
       <c r="R13">
         <v>6</v>
+      </c>
+      <c r="S13">
+        <v>2</v>
       </c>
       <c r="T13" s="1">
         <v>-640.83010000000002</v>
@@ -1346,13 +1427,16 @@
         <v>25</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R14">
         <v>6</v>
+      </c>
+      <c r="S14">
+        <v>2</v>
       </c>
       <c r="T14" s="1">
         <v>-640.83010000000002</v>
@@ -1369,13 +1453,16 @@
         <v>22</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
         <v>24</v>
       </c>
       <c r="R15">
         <v>6</v>
+      </c>
+      <c r="S15">
+        <v>2</v>
       </c>
       <c r="T15" s="1">
         <v>-640.83010000000002</v>
@@ -1392,13 +1479,16 @@
         <v>22</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
         <v>24</v>
       </c>
       <c r="R16">
         <v>6</v>
+      </c>
+      <c r="S16">
+        <v>2</v>
       </c>
       <c r="T16" s="1">
         <v>-640.83010000000002</v>
@@ -1415,13 +1505,16 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R17">
         <v>6</v>
+      </c>
+      <c r="S17">
+        <v>2</v>
       </c>
       <c r="T17" s="1">
         <v>-640.83010000000002</v>
@@ -1438,13 +1531,16 @@
         <v>22</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
         <v>24</v>
       </c>
       <c r="R18">
         <v>6</v>
+      </c>
+      <c r="S18">
+        <v>2</v>
       </c>
       <c r="T18" s="1">
         <v>-640.83010000000002</v>
@@ -1461,13 +1557,16 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R19">
         <v>6</v>
+      </c>
+      <c r="S19">
+        <v>2</v>
       </c>
       <c r="T19" s="1">
         <v>-640.83010000000002</v>
@@ -1484,13 +1583,16 @@
         <v>22</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
         <v>24</v>
       </c>
       <c r="R20">
         <v>6</v>
+      </c>
+      <c r="S20">
+        <v>2</v>
       </c>
       <c r="T20" s="1">
         <v>-640.83010000000002</v>
@@ -1507,13 +1609,16 @@
         <v>22</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
         <v>24</v>
       </c>
       <c r="R21">
         <v>6</v>
+      </c>
+      <c r="S21">
+        <v>2</v>
       </c>
       <c r="T21" s="1">
         <v>-640.83010000000002</v>
@@ -1530,13 +1635,16 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R22">
         <v>6</v>
+      </c>
+      <c r="S22">
+        <v>2</v>
       </c>
       <c r="T22" s="1">
         <v>-640.83010000000002</v>
@@ -1553,13 +1661,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
         <v>24</v>
       </c>
       <c r="R23">
         <v>6</v>
+      </c>
+      <c r="S23">
+        <v>2</v>
       </c>
       <c r="T23" s="1">
         <v>-640.83010000000002</v>
@@ -1576,13 +1687,16 @@
         <v>25</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R24">
         <v>6</v>
+      </c>
+      <c r="S24">
+        <v>2</v>
       </c>
       <c r="T24" s="1">
         <v>-640.83010000000002</v>
@@ -1596,16 +1710,19 @@
     </row>
     <row r="25" spans="1:22">
       <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" t="s">
-        <v>31</v>
-      </c>
       <c r="R25">
         <v>6</v>
+      </c>
+      <c r="S25">
+        <v>2</v>
       </c>
       <c r="T25" s="1">
         <v>-640.83010000000002</v>
@@ -1622,13 +1739,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R26">
         <v>6</v>
+      </c>
+      <c r="S26">
+        <v>2</v>
       </c>
       <c r="T26" s="1">
         <v>-640.83010000000002</v>
@@ -1645,13 +1765,16 @@
         <v>22</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C27" t="s">
         <v>24</v>
       </c>
       <c r="R27">
         <v>6</v>
+      </c>
+      <c r="S27">
+        <v>2</v>
       </c>
       <c r="T27" s="1">
         <v>-640.83010000000002</v>
@@ -1668,13 +1791,16 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R28">
         <v>6</v>
+      </c>
+      <c r="S28">
+        <v>2</v>
       </c>
       <c r="T28" s="1">
         <v>-640.83010000000002</v>
@@ -1688,16 +1814,19 @@
     </row>
     <row r="29" spans="1:22">
       <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" t="s">
-        <v>31</v>
-      </c>
       <c r="R29">
         <v>6</v>
+      </c>
+      <c r="S29">
+        <v>2</v>
       </c>
       <c r="T29" s="1">
         <v>-640.83010000000002</v>
@@ -1714,7 +1843,7 @@
         <v>22</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="C30" t="s">
         <v>24</v>
@@ -1724,6 +1853,9 @@
       </c>
       <c r="R30">
         <v>6</v>
+      </c>
+      <c r="S30">
+        <v>2</v>
       </c>
       <c r="T30" s="1">
         <v>-640.83010000000002</v>
@@ -1740,14 +1872,17 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R31">
         <v>8</v>
       </c>
+      <c r="S31">
+        <v>2</v>
+      </c>
       <c r="T31" s="1">
         <v>-640.83010000000002</v>
       </c>
@@ -1760,17 +1895,20 @@
     </row>
     <row r="32" spans="1:22">
       <c r="A32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" t="s">
         <v>29</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C32" t="s">
-        <v>31</v>
       </c>
       <c r="R32">
         <v>8</v>
       </c>
+      <c r="S32">
+        <v>2</v>
+      </c>
       <c r="T32" s="1">
         <v>-640.83010000000002</v>
       </c>
@@ -1786,7 +1924,7 @@
         <v>22</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="C33" t="s">
         <v>24</v>
@@ -1794,6 +1932,9 @@
       <c r="R33">
         <v>8</v>
       </c>
+      <c r="S33">
+        <v>2</v>
+      </c>
       <c r="T33" s="1">
         <v>-640.83010000000002</v>
       </c>
@@ -1806,17 +1947,20 @@
     </row>
     <row r="34" spans="1:22">
       <c r="A34" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" t="s">
         <v>29</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C34" t="s">
-        <v>31</v>
       </c>
       <c r="R34">
         <v>8</v>
       </c>
+      <c r="S34">
+        <v>2</v>
+      </c>
       <c r="T34" s="1">
         <v>-640.83010000000002</v>
       </c>
@@ -1832,13 +1976,16 @@
         <v>22</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="C35" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="R35">
         <v>8</v>
+      </c>
+      <c r="S35">
+        <v>2</v>
       </c>
       <c r="T35" s="1">
         <v>-640.83010000000002</v>
@@ -1855,14 +2002,17 @@
         <v>25</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R36">
         <v>8</v>
       </c>
+      <c r="S36">
+        <v>2</v>
+      </c>
       <c r="T36" s="1">
         <v>-640.83010000000002</v>
       </c>
@@ -1875,17 +2025,20 @@
     </row>
     <row r="37" spans="1:22">
       <c r="A37" t="s">
+        <v>28</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" t="s">
         <v>29</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C37" t="s">
-        <v>31</v>
       </c>
       <c r="R37">
         <v>8</v>
       </c>
+      <c r="S37">
+        <v>2</v>
+      </c>
       <c r="T37" s="1">
         <v>-640.83010000000002</v>
       </c>
@@ -1898,17 +2051,20 @@
     </row>
     <row r="38" spans="1:22">
       <c r="A38" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" t="s">
         <v>29</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C38" t="s">
-        <v>31</v>
       </c>
       <c r="R38">
         <v>8</v>
       </c>
+      <c r="S38">
+        <v>2</v>
+      </c>
       <c r="T38" s="1">
         <v>-640.83010000000002</v>
       </c>
@@ -1924,13 +2080,16 @@
         <v>22</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="C39" t="s">
         <v>24</v>
       </c>
       <c r="R39">
         <v>8</v>
+      </c>
+      <c r="S39">
+        <v>2</v>
       </c>
       <c r="T39" s="1">
         <v>-640.83010000000002</v>
@@ -1947,14 +2106,17 @@
         <v>25</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="C40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R40">
         <v>8</v>
       </c>
+      <c r="S40">
+        <v>2</v>
+      </c>
       <c r="T40" s="1">
         <v>-640.83010000000002</v>
       </c>
@@ -1967,17 +2129,20 @@
     </row>
     <row r="41" spans="1:22">
       <c r="A41" t="s">
+        <v>28</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C41" t="s">
         <v>29</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C41" t="s">
-        <v>31</v>
       </c>
       <c r="R41">
         <v>8</v>
       </c>
+      <c r="S41">
+        <v>2</v>
+      </c>
       <c r="T41" s="1">
         <v>-640.83010000000002</v>
       </c>
@@ -1993,7 +2158,7 @@
         <v>22</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="C42" t="s">
         <v>24</v>
@@ -2001,6 +2166,9 @@
       <c r="R42">
         <v>8</v>
       </c>
+      <c r="S42">
+        <v>2</v>
+      </c>
       <c r="T42" s="1">
         <v>-640.83010000000002</v>
       </c>
@@ -2016,7 +2184,7 @@
         <v>22</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="C43" t="s">
         <v>24</v>
@@ -2024,6 +2192,9 @@
       <c r="R43">
         <v>8</v>
       </c>
+      <c r="S43">
+        <v>2</v>
+      </c>
       <c r="T43" s="1">
         <v>-640.83010000000002</v>
       </c>
@@ -2039,13 +2210,16 @@
         <v>22</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="C44" t="s">
         <v>24</v>
       </c>
       <c r="R44">
         <v>8</v>
+      </c>
+      <c r="S44">
+        <v>2</v>
       </c>
       <c r="T44" s="1">
         <v>-640.83010000000002</v>
@@ -2062,14 +2236,17 @@
         <v>25</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="C45" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R45">
         <v>8</v>
       </c>
+      <c r="S45">
+        <v>2</v>
+      </c>
       <c r="T45" s="1">
         <v>-640.83010000000002</v>
       </c>
@@ -2082,17 +2259,20 @@
     </row>
     <row r="46" spans="1:22">
       <c r="A46" t="s">
+        <v>28</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C46" t="s">
         <v>29</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C46" t="s">
-        <v>31</v>
       </c>
       <c r="R46">
         <v>8</v>
       </c>
+      <c r="S46">
+        <v>2</v>
+      </c>
       <c r="T46" s="1">
         <v>-640.83010000000002</v>
       </c>
@@ -2108,7 +2288,7 @@
         <v>22</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="C47" t="s">
         <v>24</v>
@@ -2116,6 +2296,9 @@
       <c r="R47">
         <v>8</v>
       </c>
+      <c r="S47">
+        <v>2</v>
+      </c>
       <c r="T47" s="1">
         <v>-640.83010000000002</v>
       </c>
@@ -2131,7 +2314,7 @@
         <v>22</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="C48" t="s">
         <v>24</v>
@@ -2142,6 +2325,9 @@
       <c r="R48">
         <v>8</v>
       </c>
+      <c r="S48">
+        <v>2</v>
+      </c>
       <c r="T48" s="1">
         <v>-640.83010000000002</v>
       </c>
@@ -2157,13 +2343,16 @@
         <v>22</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="C49" t="s">
         <v>24</v>
       </c>
       <c r="R49">
         <v>6</v>
+      </c>
+      <c r="S49">
+        <v>2</v>
       </c>
       <c r="T49" s="1">
         <v>-640.83010000000002</v>
@@ -2180,13 +2369,16 @@
         <v>25</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="C50" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R50">
         <v>6</v>
+      </c>
+      <c r="S50">
+        <v>2</v>
       </c>
       <c r="T50" s="1">
         <v>-640.83010000000002</v>
@@ -2203,13 +2395,16 @@
         <v>22</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="C51" t="s">
         <v>24</v>
       </c>
       <c r="R51">
         <v>6</v>
+      </c>
+      <c r="S51">
+        <v>2</v>
       </c>
       <c r="T51" s="1">
         <v>-640.83010000000002</v>
@@ -2226,13 +2421,16 @@
         <v>22</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="C52" t="s">
         <v>24</v>
       </c>
       <c r="R52">
         <v>6</v>
+      </c>
+      <c r="S52">
+        <v>2</v>
       </c>
       <c r="T52" s="1">
         <v>-640.83010000000002</v>
@@ -2249,13 +2447,16 @@
         <v>25</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="C53" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R53">
         <v>6</v>
+      </c>
+      <c r="S53">
+        <v>2</v>
       </c>
       <c r="T53" s="1">
         <v>-640.83010000000002</v>
@@ -2272,13 +2473,16 @@
         <v>22</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="C54" t="s">
         <v>24</v>
       </c>
       <c r="R54">
         <v>6</v>
+      </c>
+      <c r="S54">
+        <v>2</v>
       </c>
       <c r="T54" s="1">
         <v>-640.83010000000002</v>
@@ -2292,16 +2496,19 @@
     </row>
     <row r="55" spans="1:22">
       <c r="A55" t="s">
+        <v>28</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C55" t="s">
         <v>29</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C55" t="s">
-        <v>31</v>
-      </c>
       <c r="R55">
         <v>6</v>
+      </c>
+      <c r="S55">
+        <v>2</v>
       </c>
       <c r="T55" s="1">
         <v>-640.83010000000002</v>
@@ -2318,13 +2525,16 @@
         <v>22</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C56" t="s">
         <v>24</v>
       </c>
       <c r="R56">
         <v>6</v>
+      </c>
+      <c r="S56">
+        <v>2</v>
       </c>
       <c r="T56" s="1">
         <v>-640.83010000000002</v>
@@ -2338,16 +2548,19 @@
     </row>
     <row r="57" spans="1:22">
       <c r="A57" t="s">
+        <v>28</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C57" t="s">
         <v>29</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C57" t="s">
-        <v>31</v>
-      </c>
       <c r="R57">
         <v>6</v>
+      </c>
+      <c r="S57">
+        <v>2</v>
       </c>
       <c r="T57" s="1">
         <v>-640.83010000000002</v>
@@ -2364,13 +2577,16 @@
         <v>22</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C58" t="s">
         <v>24</v>
       </c>
       <c r="R58">
         <v>6</v>
+      </c>
+      <c r="S58">
+        <v>2</v>
       </c>
       <c r="T58" s="1">
         <v>-640.83010000000002</v>
@@ -2387,13 +2603,16 @@
         <v>22</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="C59" t="s">
         <v>24</v>
       </c>
       <c r="R59">
         <v>6</v>
+      </c>
+      <c r="S59">
+        <v>2</v>
       </c>
       <c r="T59" s="1">
         <v>-640.83010000000002</v>
@@ -2410,13 +2629,16 @@
         <v>22</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="C60" t="s">
         <v>24</v>
       </c>
       <c r="R60">
         <v>6</v>
+      </c>
+      <c r="S60">
+        <v>2</v>
       </c>
       <c r="T60" s="1">
         <v>-640.83010000000002</v>
@@ -2433,13 +2655,16 @@
         <v>25</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="C61" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R61">
         <v>6</v>
+      </c>
+      <c r="S61">
+        <v>2</v>
       </c>
       <c r="T61" s="1">
         <v>-640.83010000000002</v>
@@ -2456,13 +2681,16 @@
         <v>22</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="C62" t="s">
         <v>24</v>
       </c>
       <c r="R62">
         <v>6</v>
+      </c>
+      <c r="S62">
+        <v>2</v>
       </c>
       <c r="T62" s="1">
         <v>-640.83010000000002</v>
@@ -2479,13 +2707,16 @@
         <v>22</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="C63" t="s">
         <v>24</v>
       </c>
       <c r="R63">
         <v>6</v>
+      </c>
+      <c r="S63">
+        <v>2</v>
       </c>
       <c r="T63" s="1">
         <v>-640.83010000000002</v>
@@ -2502,13 +2733,16 @@
         <v>22</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="C64" t="s">
         <v>24</v>
       </c>
       <c r="R64">
         <v>6</v>
+      </c>
+      <c r="S64">
+        <v>2</v>
       </c>
       <c r="T64" s="1">
         <v>-640.83010000000002</v>
@@ -2525,13 +2759,16 @@
         <v>22</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="C65" t="s">
         <v>24</v>
       </c>
       <c r="R65">
         <v>6</v>
+      </c>
+      <c r="S65">
+        <v>2</v>
       </c>
       <c r="T65" s="1">
         <v>-640.83010000000002</v>
@@ -2548,13 +2785,16 @@
         <v>25</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="C66" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R66">
         <v>6</v>
+      </c>
+      <c r="S66">
+        <v>2</v>
       </c>
       <c r="T66" s="1">
         <v>-640.83010000000002</v>
@@ -2571,13 +2811,16 @@
         <v>22</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="C67" t="s">
         <v>24</v>
       </c>
       <c r="R67">
         <v>6</v>
+      </c>
+      <c r="S67">
+        <v>2</v>
       </c>
       <c r="T67" s="1">
         <v>-640.83010000000002</v>
@@ -2594,13 +2837,16 @@
         <v>22</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="C68" t="s">
         <v>24</v>
       </c>
       <c r="R68">
         <v>6</v>
+      </c>
+      <c r="S68">
+        <v>2</v>
       </c>
       <c r="T68" s="1">
         <v>-640.83010000000002</v>
@@ -2617,13 +2863,16 @@
         <v>25</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="C69" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R69">
         <v>6</v>
+      </c>
+      <c r="S69">
+        <v>2</v>
       </c>
       <c r="T69" s="1">
         <v>-640.83010000000002</v>
@@ -2640,13 +2889,16 @@
         <v>22</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="C70" t="s">
         <v>24</v>
       </c>
       <c r="R70">
         <v>6</v>
+      </c>
+      <c r="S70">
+        <v>2</v>
       </c>
       <c r="T70" s="1">
         <v>-640.83010000000002</v>
@@ -2663,13 +2915,16 @@
         <v>25</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="C71" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R71">
         <v>6</v>
+      </c>
+      <c r="S71">
+        <v>2</v>
       </c>
       <c r="T71" s="1">
         <v>-640.83010000000002</v>
@@ -2686,13 +2941,16 @@
         <v>22</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="C72" t="s">
         <v>24</v>
       </c>
       <c r="R72">
         <v>6</v>
+      </c>
+      <c r="S72">
+        <v>2</v>
       </c>
       <c r="T72" s="1">
         <v>-640.83010000000002</v>
@@ -2709,13 +2967,16 @@
         <v>25</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="C73" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R73">
         <v>6</v>
+      </c>
+      <c r="S73">
+        <v>2</v>
       </c>
       <c r="T73" s="1">
         <v>-640.83010000000002</v>
@@ -2729,16 +2990,19 @@
     </row>
     <row r="74" spans="1:22">
       <c r="A74" t="s">
+        <v>28</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C74" t="s">
         <v>29</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C74" t="s">
-        <v>31</v>
-      </c>
       <c r="R74">
         <v>6</v>
+      </c>
+      <c r="S74">
+        <v>2</v>
       </c>
       <c r="T74" s="1">
         <v>-640.83010000000002</v>
@@ -2755,13 +3019,16 @@
         <v>25</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="C75" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R75">
         <v>6</v>
+      </c>
+      <c r="S75">
+        <v>2</v>
       </c>
       <c r="T75" s="1">
         <v>-640.83010000000002</v>
@@ -2778,13 +3045,16 @@
         <v>22</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="C76" t="s">
         <v>24</v>
       </c>
       <c r="R76">
         <v>6</v>
+      </c>
+      <c r="S76">
+        <v>2</v>
       </c>
       <c r="T76" s="1">
         <v>-640.83010000000002</v>
@@ -2801,13 +3071,16 @@
         <v>25</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="C77" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R77">
         <v>6</v>
+      </c>
+      <c r="S77">
+        <v>2</v>
       </c>
       <c r="T77" s="1">
         <v>-640.83010000000002</v>
@@ -2824,13 +3097,16 @@
         <v>22</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="C78" t="s">
         <v>24</v>
       </c>
       <c r="R78">
         <v>6</v>
+      </c>
+      <c r="S78">
+        <v>2</v>
       </c>
       <c r="T78" s="1">
         <v>-640.83010000000002</v>
@@ -2847,13 +3123,16 @@
         <v>22</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="C79" t="s">
         <v>24</v>
       </c>
       <c r="R79">
         <v>6</v>
+      </c>
+      <c r="S79">
+        <v>2</v>
       </c>
       <c r="T79" s="1">
         <v>-640.83010000000002</v>
@@ -2867,25 +3146,28 @@
     </row>
     <row r="80" spans="1:22">
       <c r="A80" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C80" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>124</v>
+        <v>76</v>
       </c>
       <c r="P80" s="1">
         <v>570</v>
       </c>
       <c r="Q80" s="5" t="s">
-        <v>126</v>
+        <v>78</v>
       </c>
       <c r="R80">
         <v>6</v>
+      </c>
+      <c r="S80">
+        <v>2</v>
       </c>
       <c r="T80" s="1">
         <v>-640.83010000000002</v>
@@ -2902,13 +3184,16 @@
         <v>22</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="C81" t="s">
         <v>24</v>
       </c>
       <c r="R81">
         <v>6</v>
+      </c>
+      <c r="S81">
+        <v>2</v>
       </c>
       <c r="T81" s="1">
         <v>-640.83010000000002</v>
@@ -2925,13 +3210,16 @@
         <v>25</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="C82" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R82">
         <v>6</v>
+      </c>
+      <c r="S82">
+        <v>2</v>
       </c>
       <c r="T82" s="1">
         <v>-640.83010000000002</v>
@@ -2945,16 +3233,19 @@
     </row>
     <row r="83" spans="1:22">
       <c r="A83" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="C83" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="R83">
         <v>6</v>
+      </c>
+      <c r="S83">
+        <v>2</v>
       </c>
       <c r="T83" s="1">
         <v>-640.83010000000002</v>
@@ -2968,16 +3259,19 @@
     </row>
     <row r="84" spans="1:22">
       <c r="A84" t="s">
+        <v>28</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C84" t="s">
         <v>29</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C84" t="s">
-        <v>31</v>
-      </c>
       <c r="R84">
         <v>6</v>
+      </c>
+      <c r="S84">
+        <v>2</v>
       </c>
       <c r="T84" s="1">
         <v>-640.83010000000002</v>
@@ -2991,16 +3285,19 @@
     </row>
     <row r="85" spans="1:22">
       <c r="A85" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C85" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="R85">
         <v>6</v>
+      </c>
+      <c r="S85">
+        <v>2</v>
       </c>
       <c r="T85" s="1">
         <v>-640.83010000000002</v>
@@ -3017,13 +3314,16 @@
         <v>22</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="C86" t="s">
         <v>24</v>
       </c>
       <c r="R86">
         <v>6</v>
+      </c>
+      <c r="S86">
+        <v>2</v>
       </c>
       <c r="T86" s="1">
         <v>-640.83010000000002</v>
@@ -3037,16 +3337,19 @@
     </row>
     <row r="87" spans="1:22">
       <c r="A87" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C87" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="R87">
         <v>6</v>
+      </c>
+      <c r="S87">
+        <v>2</v>
       </c>
       <c r="T87" s="1">
         <v>-640.83010000000002</v>
@@ -3063,13 +3366,16 @@
         <v>22</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="C88" t="s">
         <v>24</v>
       </c>
       <c r="R88">
         <v>6</v>
+      </c>
+      <c r="S88">
+        <v>2</v>
       </c>
       <c r="T88" s="1">
         <v>-640.83010000000002</v>
@@ -3086,13 +3392,16 @@
         <v>25</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C89" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R89">
         <v>6</v>
+      </c>
+      <c r="S89">
+        <v>2</v>
       </c>
       <c r="T89" s="1">
         <v>-640.83010000000002</v>
@@ -3106,25 +3415,28 @@
     </row>
     <row r="90" spans="1:22">
       <c r="A90" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="O90" s="4" t="s">
-        <v>124</v>
+        <v>76</v>
       </c>
       <c r="P90" s="1">
         <v>570</v>
       </c>
       <c r="Q90" s="5" t="s">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="R90">
         <v>6</v>
+      </c>
+      <c r="S90">
+        <v>2</v>
       </c>
       <c r="T90" s="1">
         <v>-640.83010000000002</v>
@@ -3141,13 +3453,16 @@
         <v>25</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="C91" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R91">
         <v>6</v>
+      </c>
+      <c r="S91">
+        <v>2</v>
       </c>
       <c r="T91" s="1">
         <v>-640.83010000000002</v>
@@ -3161,16 +3476,19 @@
     </row>
     <row r="92" spans="1:22">
       <c r="A92" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="R92">
         <v>6</v>
+      </c>
+      <c r="S92">
+        <v>2</v>
       </c>
       <c r="T92" s="1">
         <v>-640.83010000000002</v>
@@ -3187,13 +3505,16 @@
         <v>22</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="C93" t="s">
         <v>24</v>
       </c>
       <c r="R93">
         <v>6</v>
+      </c>
+      <c r="S93">
+        <v>2</v>
       </c>
       <c r="T93" s="1">
         <v>-640.83010000000002</v>
@@ -3207,16 +3528,19 @@
     </row>
     <row r="94" spans="1:22">
       <c r="A94" t="s">
+        <v>28</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C94" t="s">
         <v>29</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C94" t="s">
-        <v>31</v>
-      </c>
       <c r="R94">
         <v>6</v>
+      </c>
+      <c r="S94">
+        <v>2</v>
       </c>
       <c r="T94" s="1">
         <v>-640.83010000000002</v>
@@ -3233,13 +3557,16 @@
         <v>25</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C95" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R95">
         <v>6</v>
+      </c>
+      <c r="S95">
+        <v>2</v>
       </c>
       <c r="T95" s="1">
         <v>-640.83010000000002</v>
@@ -3253,16 +3580,19 @@
     </row>
     <row r="96" spans="1:22">
       <c r="A96" t="s">
+        <v>28</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C96" t="s">
         <v>29</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C96" t="s">
-        <v>31</v>
-      </c>
       <c r="R96">
         <v>6</v>
+      </c>
+      <c r="S96">
+        <v>2</v>
       </c>
       <c r="T96" s="1">
         <v>-640.83010000000002</v>
@@ -3279,13 +3609,16 @@
         <v>22</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="C97" t="s">
         <v>24</v>
       </c>
       <c r="R97">
         <v>6</v>
+      </c>
+      <c r="S97">
+        <v>2</v>
       </c>
       <c r="T97" s="1">
         <v>-640.83010000000002</v>
@@ -3299,16 +3632,19 @@
     </row>
     <row r="98" spans="1:22">
       <c r="A98" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="R98">
         <v>6</v>
+      </c>
+      <c r="S98">
+        <v>2</v>
       </c>
       <c r="T98" s="1">
         <v>-640.83010000000002</v>
@@ -3322,7 +3658,7 @@
     </row>
     <row r="99" spans="1:22">
       <c r="A99" s="5" t="s">
-        <v>127</v>
+        <v>79</v>
       </c>
       <c r="B99">
         <v>12</v>

--- a/TextGame project/Assets/Resources/Story/11.xlsx
+++ b/TextGame project/Assets/Resources/Story/11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C0D1708-9729-4C3F-B9C0-D1BCDAC3BA43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CBB505E-186B-45DD-8549-130CD2A35512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1138,7 +1138,7 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>77</v>
@@ -1176,7 +1176,7 @@
         <v>6</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T4" s="1">
         <v>-640.83010000000002</v>
@@ -1202,7 +1202,7 @@
         <v>6</v>
       </c>
       <c r="S5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T5" s="1">
         <v>-640.83010000000002</v>
@@ -1228,7 +1228,7 @@
         <v>6</v>
       </c>
       <c r="S6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T6" s="1">
         <v>-640.83010000000002</v>
@@ -1254,7 +1254,7 @@
         <v>6</v>
       </c>
       <c r="S7">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T7" s="1">
         <v>-640.83010000000002</v>
@@ -1280,7 +1280,7 @@
         <v>6</v>
       </c>
       <c r="S8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T8" s="1">
         <v>-640.83010000000002</v>
@@ -1306,7 +1306,7 @@
         <v>6</v>
       </c>
       <c r="S9">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T9" s="1">
         <v>-640.83010000000002</v>
@@ -1332,7 +1332,7 @@
         <v>6</v>
       </c>
       <c r="S10">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T10" s="1">
         <v>-640.83010000000002</v>
@@ -1358,7 +1358,7 @@
         <v>6</v>
       </c>
       <c r="S11">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T11" s="1">
         <v>-640.83010000000002</v>
@@ -1384,7 +1384,7 @@
         <v>6</v>
       </c>
       <c r="S12">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T12" s="1">
         <v>-640.83010000000002</v>
@@ -1410,7 +1410,7 @@
         <v>6</v>
       </c>
       <c r="S13">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T13" s="1">
         <v>-640.83010000000002</v>
@@ -1436,7 +1436,7 @@
         <v>6</v>
       </c>
       <c r="S14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T14" s="1">
         <v>-640.83010000000002</v>
@@ -1462,7 +1462,7 @@
         <v>6</v>
       </c>
       <c r="S15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T15" s="1">
         <v>-640.83010000000002</v>
@@ -1488,7 +1488,7 @@
         <v>6</v>
       </c>
       <c r="S16">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T16" s="1">
         <v>-640.83010000000002</v>
@@ -1514,7 +1514,7 @@
         <v>6</v>
       </c>
       <c r="S17">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T17" s="1">
         <v>-640.83010000000002</v>
@@ -1540,7 +1540,7 @@
         <v>6</v>
       </c>
       <c r="S18">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T18" s="1">
         <v>-640.83010000000002</v>
@@ -1566,7 +1566,7 @@
         <v>6</v>
       </c>
       <c r="S19">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T19" s="1">
         <v>-640.83010000000002</v>
@@ -1592,7 +1592,7 @@
         <v>6</v>
       </c>
       <c r="S20">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T20" s="1">
         <v>-640.83010000000002</v>
@@ -1618,7 +1618,7 @@
         <v>6</v>
       </c>
       <c r="S21">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T21" s="1">
         <v>-640.83010000000002</v>
@@ -1644,7 +1644,7 @@
         <v>6</v>
       </c>
       <c r="S22">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T22" s="1">
         <v>-640.83010000000002</v>
@@ -1670,7 +1670,7 @@
         <v>6</v>
       </c>
       <c r="S23">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T23" s="1">
         <v>-640.83010000000002</v>
@@ -1696,7 +1696,7 @@
         <v>6</v>
       </c>
       <c r="S24">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T24" s="1">
         <v>-640.83010000000002</v>
@@ -1722,7 +1722,7 @@
         <v>6</v>
       </c>
       <c r="S25">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T25" s="1">
         <v>-640.83010000000002</v>
@@ -1748,7 +1748,7 @@
         <v>6</v>
       </c>
       <c r="S26">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T26" s="1">
         <v>-640.83010000000002</v>
@@ -1774,7 +1774,7 @@
         <v>6</v>
       </c>
       <c r="S27">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T27" s="1">
         <v>-640.83010000000002</v>
@@ -1800,7 +1800,7 @@
         <v>6</v>
       </c>
       <c r="S28">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T28" s="1">
         <v>-640.83010000000002</v>
@@ -1826,7 +1826,7 @@
         <v>6</v>
       </c>
       <c r="S29">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T29" s="1">
         <v>-640.83010000000002</v>
@@ -1855,7 +1855,7 @@
         <v>6</v>
       </c>
       <c r="S30">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T30" s="1">
         <v>-640.83010000000002</v>
@@ -1881,7 +1881,7 @@
         <v>8</v>
       </c>
       <c r="S31">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T31" s="1">
         <v>-640.83010000000002</v>
@@ -1907,7 +1907,7 @@
         <v>8</v>
       </c>
       <c r="S32">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T32" s="1">
         <v>-640.83010000000002</v>
@@ -1933,7 +1933,7 @@
         <v>8</v>
       </c>
       <c r="S33">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T33" s="1">
         <v>-640.83010000000002</v>
@@ -1959,7 +1959,7 @@
         <v>8</v>
       </c>
       <c r="S34">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T34" s="1">
         <v>-640.83010000000002</v>
@@ -1985,7 +1985,7 @@
         <v>8</v>
       </c>
       <c r="S35">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T35" s="1">
         <v>-640.83010000000002</v>
@@ -2011,7 +2011,7 @@
         <v>8</v>
       </c>
       <c r="S36">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T36" s="1">
         <v>-640.83010000000002</v>
@@ -2037,7 +2037,7 @@
         <v>8</v>
       </c>
       <c r="S37">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T37" s="1">
         <v>-640.83010000000002</v>
@@ -2063,7 +2063,7 @@
         <v>8</v>
       </c>
       <c r="S38">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T38" s="1">
         <v>-640.83010000000002</v>
@@ -2089,7 +2089,7 @@
         <v>8</v>
       </c>
       <c r="S39">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T39" s="1">
         <v>-640.83010000000002</v>
@@ -2115,7 +2115,7 @@
         <v>8</v>
       </c>
       <c r="S40">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T40" s="1">
         <v>-640.83010000000002</v>
@@ -2141,7 +2141,7 @@
         <v>8</v>
       </c>
       <c r="S41">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T41" s="1">
         <v>-640.83010000000002</v>
@@ -2167,7 +2167,7 @@
         <v>8</v>
       </c>
       <c r="S42">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T42" s="1">
         <v>-640.83010000000002</v>
@@ -2193,7 +2193,7 @@
         <v>8</v>
       </c>
       <c r="S43">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T43" s="1">
         <v>-640.83010000000002</v>
@@ -2219,7 +2219,7 @@
         <v>8</v>
       </c>
       <c r="S44">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T44" s="1">
         <v>-640.83010000000002</v>
@@ -2245,7 +2245,7 @@
         <v>8</v>
       </c>
       <c r="S45">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T45" s="1">
         <v>-640.83010000000002</v>
@@ -2271,7 +2271,7 @@
         <v>8</v>
       </c>
       <c r="S46">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T46" s="1">
         <v>-640.83010000000002</v>
@@ -2293,11 +2293,14 @@
       <c r="C47" t="s">
         <v>24</v>
       </c>
+      <c r="F47">
+        <v>5</v>
+      </c>
       <c r="R47">
         <v>8</v>
       </c>
       <c r="S47">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T47" s="1">
         <v>-640.83010000000002</v>
@@ -2326,7 +2329,7 @@
         <v>8</v>
       </c>
       <c r="S48">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T48" s="1">
         <v>-640.83010000000002</v>
@@ -2352,7 +2355,7 @@
         <v>6</v>
       </c>
       <c r="S49">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T49" s="1">
         <v>-640.83010000000002</v>
@@ -2378,7 +2381,7 @@
         <v>6</v>
       </c>
       <c r="S50">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T50" s="1">
         <v>-640.83010000000002</v>
@@ -2404,7 +2407,7 @@
         <v>6</v>
       </c>
       <c r="S51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T51" s="1">
         <v>-640.83010000000002</v>
@@ -2430,7 +2433,7 @@
         <v>6</v>
       </c>
       <c r="S52">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T52" s="1">
         <v>-640.83010000000002</v>
@@ -2456,7 +2459,7 @@
         <v>6</v>
       </c>
       <c r="S53">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T53" s="1">
         <v>-640.83010000000002</v>
@@ -2482,7 +2485,7 @@
         <v>6</v>
       </c>
       <c r="S54">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T54" s="1">
         <v>-640.83010000000002</v>
@@ -2508,7 +2511,7 @@
         <v>6</v>
       </c>
       <c r="S55">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T55" s="1">
         <v>-640.83010000000002</v>
@@ -2534,7 +2537,7 @@
         <v>6</v>
       </c>
       <c r="S56">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T56" s="1">
         <v>-640.83010000000002</v>
@@ -2560,7 +2563,7 @@
         <v>6</v>
       </c>
       <c r="S57">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T57" s="1">
         <v>-640.83010000000002</v>
@@ -2586,7 +2589,7 @@
         <v>6</v>
       </c>
       <c r="S58">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T58" s="1">
         <v>-640.83010000000002</v>
@@ -2612,7 +2615,7 @@
         <v>6</v>
       </c>
       <c r="S59">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T59" s="1">
         <v>-640.83010000000002</v>
@@ -2638,7 +2641,7 @@
         <v>6</v>
       </c>
       <c r="S60">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T60" s="1">
         <v>-640.83010000000002</v>
@@ -2664,7 +2667,7 @@
         <v>6</v>
       </c>
       <c r="S61">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T61" s="1">
         <v>-640.83010000000002</v>
@@ -2690,7 +2693,7 @@
         <v>6</v>
       </c>
       <c r="S62">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T62" s="1">
         <v>-640.83010000000002</v>
@@ -2716,7 +2719,7 @@
         <v>6</v>
       </c>
       <c r="S63">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T63" s="1">
         <v>-640.83010000000002</v>
@@ -2742,7 +2745,7 @@
         <v>6</v>
       </c>
       <c r="S64">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T64" s="1">
         <v>-640.83010000000002</v>
@@ -2768,7 +2771,7 @@
         <v>6</v>
       </c>
       <c r="S65">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T65" s="1">
         <v>-640.83010000000002</v>
@@ -2794,7 +2797,7 @@
         <v>6</v>
       </c>
       <c r="S66">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T66" s="1">
         <v>-640.83010000000002</v>
@@ -2820,7 +2823,7 @@
         <v>6</v>
       </c>
       <c r="S67">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T67" s="1">
         <v>-640.83010000000002</v>
@@ -2846,7 +2849,7 @@
         <v>6</v>
       </c>
       <c r="S68">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T68" s="1">
         <v>-640.83010000000002</v>
@@ -2872,7 +2875,7 @@
         <v>6</v>
       </c>
       <c r="S69">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T69" s="1">
         <v>-640.83010000000002</v>
@@ -2898,7 +2901,7 @@
         <v>6</v>
       </c>
       <c r="S70">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T70" s="1">
         <v>-640.83010000000002</v>
@@ -2924,7 +2927,7 @@
         <v>6</v>
       </c>
       <c r="S71">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T71" s="1">
         <v>-640.83010000000002</v>
@@ -2950,7 +2953,7 @@
         <v>6</v>
       </c>
       <c r="S72">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T72" s="1">
         <v>-640.83010000000002</v>
@@ -2976,7 +2979,7 @@
         <v>6</v>
       </c>
       <c r="S73">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T73" s="1">
         <v>-640.83010000000002</v>
@@ -3002,7 +3005,7 @@
         <v>6</v>
       </c>
       <c r="S74">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T74" s="1">
         <v>-640.83010000000002</v>
@@ -3028,7 +3031,7 @@
         <v>6</v>
       </c>
       <c r="S75">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T75" s="1">
         <v>-640.83010000000002</v>
@@ -3050,11 +3053,14 @@
       <c r="C76" t="s">
         <v>24</v>
       </c>
+      <c r="F76">
+        <v>2</v>
+      </c>
       <c r="R76">
         <v>6</v>
       </c>
       <c r="S76">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T76" s="1">
         <v>-640.83010000000002</v>

--- a/TextGame project/Assets/Resources/Story/11.xlsx
+++ b/TextGame project/Assets/Resources/Story/11.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CBB505E-186B-45DD-8549-130CD2A35512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843CBF7F-EDC2-4DEE-AD64-2EA980D21C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="134">
   <si>
     <t>Name</t>
   </si>
@@ -478,6 +478,18 @@
   </si>
   <si>
     <t>（微笑着）两个小朋友，玩够了吗？</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qianye2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qianye1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qianye</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -544,7 +556,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -561,6 +573,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1149,8 +1162,8 @@
       <c r="J3" s="1">
         <v>-640.83010000000002</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>26</v>
+      <c r="K3" s="6" t="s">
+        <v>131</v>
       </c>
       <c r="L3" s="4" t="s">
         <v>76</v>
@@ -1169,8 +1182,8 @@
       <c r="B4" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C4" t="s">
-        <v>26</v>
+      <c r="C4" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="R4">
         <v>6</v>
@@ -1299,8 +1312,8 @@
       <c r="B9" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C9" t="s">
-        <v>26</v>
+      <c r="C9" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="R9">
         <v>6</v>
@@ -1351,8 +1364,8 @@
       <c r="B11" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C11" t="s">
-        <v>26</v>
+      <c r="C11" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="R11">
         <v>6</v>
@@ -1432,6 +1445,15 @@
       <c r="C14" t="s">
         <v>26</v>
       </c>
+      <c r="I14" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="J14" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>133</v>
+      </c>
       <c r="R14">
         <v>6</v>
       </c>
@@ -1507,8 +1529,17 @@
       <c r="B17" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C17" t="s">
-        <v>26</v>
+      <c r="C17" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="J17" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>131</v>
       </c>
       <c r="R17">
         <v>6</v>
@@ -1559,8 +1590,8 @@
       <c r="B19" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C19" t="s">
-        <v>26</v>
+      <c r="C19" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="R19">
         <v>6</v>
@@ -1637,8 +1668,8 @@
       <c r="B22" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C22" t="s">
-        <v>26</v>
+      <c r="C22" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="R22">
         <v>6</v>
@@ -1689,8 +1720,8 @@
       <c r="B24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C24" t="s">
-        <v>26</v>
+      <c r="C24" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="R24">
         <v>6</v>
@@ -1741,8 +1772,8 @@
       <c r="B26" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C26" t="s">
-        <v>26</v>
+      <c r="C26" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="R26">
         <v>6</v>
@@ -1796,6 +1827,15 @@
       <c r="C28" t="s">
         <v>26</v>
       </c>
+      <c r="I28" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="J28" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>133</v>
+      </c>
       <c r="R28">
         <v>6</v>
       </c>
@@ -2374,8 +2414,17 @@
       <c r="B50" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C50" t="s">
-        <v>26</v>
+      <c r="C50" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="J50" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>131</v>
       </c>
       <c r="R50">
         <v>6</v>
@@ -2452,8 +2501,8 @@
       <c r="B53" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C53" t="s">
-        <v>26</v>
+      <c r="C53" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="R53">
         <v>6</v>
@@ -2660,8 +2709,8 @@
       <c r="B61" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C61" t="s">
-        <v>26</v>
+      <c r="C61" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="R61">
         <v>6</v>
@@ -2790,8 +2839,8 @@
       <c r="B66" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C66" t="s">
-        <v>26</v>
+      <c r="C66" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="R66">
         <v>6</v>
@@ -2868,8 +2917,8 @@
       <c r="B69" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C69" t="s">
-        <v>26</v>
+      <c r="C69" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="R69">
         <v>6</v>
@@ -2920,8 +2969,8 @@
       <c r="B71" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C71" t="s">
-        <v>26</v>
+      <c r="C71" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="R71">
         <v>6</v>
@@ -2972,8 +3021,8 @@
       <c r="B73" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C73" t="s">
-        <v>26</v>
+      <c r="C73" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="R73">
         <v>6</v>
@@ -3024,8 +3073,8 @@
       <c r="B75" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C75" t="s">
-        <v>26</v>
+      <c r="C75" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="R75">
         <v>6</v>
@@ -3079,8 +3128,8 @@
       <c r="B77" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C77" t="s">
-        <v>26</v>
+      <c r="C77" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="R77">
         <v>6</v>
@@ -3218,8 +3267,8 @@
       <c r="B82" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C82" t="s">
-        <v>26</v>
+      <c r="C82" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="R82">
         <v>6</v>
@@ -3400,8 +3449,8 @@
       <c r="B89" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C89" t="s">
-        <v>26</v>
+      <c r="C89" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="R89">
         <v>6</v>
@@ -3461,8 +3510,17 @@
       <c r="B91" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C91" t="s">
-        <v>26</v>
+      <c r="C91" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="I91" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="J91" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K91" s="6" t="s">
+        <v>132</v>
       </c>
       <c r="R91">
         <v>6</v>
@@ -3565,8 +3623,8 @@
       <c r="B95" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C95" t="s">
-        <v>26</v>
+      <c r="C95" s="5" t="s">
+        <v>132</v>
       </c>
       <c r="R95">
         <v>6</v>
@@ -3673,7 +3731,7 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C89 C91 C93:C97 C99:C106" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C99:C106 C83:C88 C78:C81 C3 C5:C8 C10 C12:C16 C18 C20:C21 C23 C25 C27:C49 C51:C52 C54:C60 C62:C65 C67:C68 C70 C72 C74 C76 C93:C94 C96:C97" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Qianye,White,Linshen,Wangshushu"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A98 A100:A157" xr:uid="{00000000-0002-0000-0000-000001000000}">
